--- a/planos_empresas/plano_empresa_00847.xlsx
+++ b/planos_empresas/plano_empresa_00847.xlsx
@@ -413,9 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>070601 - 07.06 - Colocação e instalação de tapetes, carpetes, assoalhos, cortinas, revestimentos de parede, vidros, divisórias, placas de gesso e congêneres, com material fornecido pelo tomador do serviço.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>